--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487481_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487481_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7149</v>
+        <v>9.3057</v>
       </c>
       <c r="E2" t="n">
-        <v>9.7232</v>
+        <v>10.0467</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0083</v>
+        <v>-0.741</v>
       </c>
       <c r="G2" t="n">
         <v>4.5584</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9022</v>
+        <v>-0.3114</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.31</v>
+        <v>0.0135</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.3249</v>
       </c>
       <c r="V2" t="n">
         <v>2.7086</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0846</v>
+        <v>3.6706</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4316</v>
+        <v>3.1246</v>
       </c>
       <c r="F3" t="n">
-        <v>0.653</v>
+        <v>0.546</v>
       </c>
       <c r="G3" t="n">
         <v>2.0169</v>
@@ -688,13 +688,13 @@
         <v>0.1958</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5757</v>
+        <v>0.1617</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4623</v>
+        <v>0.1553</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1134</v>
+        <v>0.0065</v>
       </c>
       <c r="V3" t="n">
         <v>1.492</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2301</v>
+        <v>2.8494</v>
       </c>
       <c r="E4" t="n">
-        <v>0.632</v>
+        <v>1.1601</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5982</v>
+        <v>1.6893</v>
       </c>
       <c r="G4" t="n">
         <v>2.0035</v>
@@ -766,13 +766,13 @@
         <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1056</v>
+        <v>0.7249</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2153</v>
+        <v>0.3129</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3208</v>
+        <v>0.412</v>
       </c>
       <c r="V4" t="n">
         <v>1.492</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3756</v>
+        <v>1.5896</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3402</v>
+        <v>1.581</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0353</v>
+        <v>0.0086</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2632</v>
@@ -844,13 +844,13 @@
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2102</v>
+        <v>0.4242</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4286</v>
+        <v>0.6693</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2184</v>
+        <v>-0.2451</v>
       </c>
       <c r="V5" t="n">
         <v>0.0576</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8209</v>
+        <v>1.4605</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.521</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3419</v>
+        <v>1.5557</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1472</v>
@@ -922,13 +922,13 @@
         <v>2.7419</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.169</v>
+        <v>-0.5293</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2923</v>
+        <v>0.1335</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8767</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>1.5495</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7101</v>
+        <v>-1.1138</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0426</v>
+        <v>-1.508</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6675</v>
+        <v>0.3942</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8349</v>
+        <v>-0.2143</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5264</v>
+        <v>0.782</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3085</v>
+        <v>-0.9963</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4473</v>
+        <v>-1.3839</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8266</v>
+        <v>0.1633</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6207</v>
+        <v>-1.5473</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2822</v>
+        <v>1.1697</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.353</v>
+        <v>0.6187</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9292</v>
+        <v>0.551</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.917</v>
+        <v>-0.1958</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1543</v>
+        <v>0.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0538</v>
+        <v>0.0049</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8763</v>
+        <v>0.0717</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9301</v>
+        <v>-0.0669</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9412</v>
+        <v>-1.492</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3905</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7651</v>
+        <v>-2.174</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0791</v>
+        <v>-1.6402</v>
       </c>
       <c r="F8" t="n">
-        <v>0.314</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2143</v>
+        <v>-0.8349</v>
       </c>
       <c r="H8" t="n">
-        <v>0.782</v>
+        <v>-0.5264</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9963</v>
+        <v>-0.3085</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3839</v>
+        <v>1.4473</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1633</v>
+        <v>0.8266</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5473</v>
+        <v>0.6207</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1697</v>
+        <v>-2.2822</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6187</v>
+        <v>-1.353</v>
       </c>
       <c r="O8" t="n">
-        <v>0.551</v>
+        <v>-0.9292</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5875</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1958</v>
+        <v>-3.917</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7834</v>
+        <v>2.1543</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6464</v>
+        <v>-0.5177</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4993</v>
+        <v>0.2788</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1471</v>
+        <v>-0.7965</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.492</v>
+        <v>0.9412</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.492</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3919</v>
+        <v>-2.5327</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.401</v>
+        <v>-2.8893</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0091</v>
+        <v>0.3566</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7548</v>
@@ -1156,13 +1156,13 @@
         <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8905</v>
+        <v>-0.0313</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3035</v>
+        <v>0.2082</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.587</v>
+        <v>-0.2395</v>
       </c>
       <c r="V9" t="n">
         <v>0.0576</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>12.359</v>
+        <v>13.0553</v>
       </c>
       <c r="E10" t="n">
-        <v>9.083299999999998</v>
+        <v>9.779699999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2757</v>
+        <v>3.2756</v>
       </c>
       <c r="G10" t="n">
         <v>4.3644</v>
@@ -1234,13 +1234,13 @@
         <v>13.7094</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7704000000000002</v>
+        <v>-0.07399999999999984</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1468</v>
+        <v>1.8432</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.9173</v>
+        <v>-1.9172</v>
       </c>
       <c r="V10" t="n">
         <v>6.8065</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4576</v>
+        <v>0.7224</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8682</v>
+        <v>0.7164</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4106</v>
+        <v>0.006</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8077</v>
+        <v>2.322</v>
       </c>
       <c r="H11" t="n">
-        <v>1.312</v>
+        <v>-0.2854</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4957</v>
+        <v>2.6073</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3317</v>
+        <v>2.8397</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5994</v>
+        <v>0.9354</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7323</v>
+        <v>1.9043</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.524</v>
+        <v>-0.5177</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2874</v>
+        <v>-1.2207</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2366</v>
+        <v>0.703</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8065</v>
+        <v>0.4787</v>
       </c>
       <c r="T11" t="n">
-        <v>2.6678</v>
+        <v>0.5011</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1388</v>
+        <v>-0.0223</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.1567</v>
+        <v>-1.8825</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.1728</v>
+        <v>-0.6659</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9839</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2403</v>
+        <v>0.5677</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9203</v>
+        <v>1.432</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.68</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>1.1503</v>
@@ -1390,13 +1390,13 @@
         <v>1.9585</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1073</v>
+        <v>0.4346</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4882</v>
+        <v>0.0235</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5954</v>
+        <v>0.4111</v>
       </c>
       <c r="V12" t="n">
         <v>0.9412</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.0424</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4094</v>
+        <v>2.2308</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4808</v>
+        <v>-2.1884</v>
       </c>
       <c r="G14" t="n">
-        <v>2.322</v>
+        <v>1.8077</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2854</v>
+        <v>1.312</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6073</v>
+        <v>0.4957</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8397</v>
+        <v>3.3317</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9354</v>
+        <v>2.5994</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9043</v>
+        <v>0.7323</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5177</v>
+        <v>-1.524</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2207</v>
+        <v>-1.2874</v>
       </c>
       <c r="O14" t="n">
-        <v>0.703</v>
+        <v>-0.2366</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.315</v>
+        <v>1.3914</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1941</v>
+        <v>1.0304</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5091</v>
+        <v>0.361</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.8825</v>
+        <v>-3.1567</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6659</v>
+        <v>-0.1728</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2166</v>
+        <v>-2.9839</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.2464</v>
+        <v>-0.4545</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5801</v>
+        <v>-1.1707</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3337</v>
+        <v>0.7163</v>
       </c>
       <c r="G15" t="n">
         <v>-1.2704</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1512</v>
+        <v>-0.3592</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6358</v>
+        <v>-0.2264</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5154</v>
+        <v>-0.1328</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0719</v>
+        <v>-1.2237</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3933</v>
+        <v>-1.5746</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3214</v>
+        <v>0.3509</v>
       </c>
       <c r="G16" t="n">
         <v>-1.7512</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1836</v>
+        <v>0.6646</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4882</v>
+        <v>0.3305</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3045</v>
+        <v>0.3341</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3329</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3352</v>
+        <v>-1.9775</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1746</v>
+        <v>1.0722</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5098</v>
+        <v>-3.0498</v>
       </c>
       <c r="G17" t="n">
         <v>-2.7235</v>
@@ -1780,13 +1780,13 @@
         <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4506</v>
+        <v>0.8082</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8169</v>
+        <v>0.7146</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3663</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8249</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-8.429399999999999</v>
+        <v>-8.086499999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.8518</v>
+        <v>-6.1588</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5776</v>
+        <v>-1.9277</v>
       </c>
       <c r="G18" t="n">
         <v>-3.9198</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8253</v>
+        <v>-0.4824</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0306</v>
+        <v>-0.3376</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7947</v>
+        <v>-0.1448</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5507</v>
@@ -1891,28 +1891,28 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-12.3589</v>
+        <v>-10.3122</v>
       </c>
       <c r="E19" t="n">
         <v>-3.551100000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.8079</v>
+        <v>-6.7613</v>
       </c>
       <c r="G19" t="n">
         <v>-4.3645</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.124499999999999</v>
+        <v>-5.1245</v>
       </c>
       <c r="I19" t="n">
         <v>0.7600999999999998</v>
       </c>
       <c r="J19" t="n">
-        <v>7.312500000000002</v>
+        <v>7.3125</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7133</v>
+        <v>4.713299999999999</v>
       </c>
       <c r="L19" t="n">
         <v>2.5993</v>
@@ -1936,19 +1936,19 @@
         <v>11.7508</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7705</v>
+        <v>2.8171</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9172</v>
+        <v>1.9173</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1468</v>
+        <v>0.9</v>
       </c>
       <c r="V19" t="n">
         <v>-6.8065</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9286999999999999</v>
+        <v>0.9287</v>
       </c>
       <c r="X19" t="n">
         <v>-7.735099999999999</v>
